--- a/outputs/secondary_synthetic_consumer/secondary_synthetic_consumer_output.xlsx
+++ b/outputs/secondary_synthetic_consumer/secondary_synthetic_consumer_output.xlsx
@@ -17,14 +17,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +49,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,9 +430,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>standardized_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_obs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>coef_retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>p_retail</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>coef_producer</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>p_producer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Молоко питне</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0006170987828229427</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5777992398736067</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.943225223379526</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.577082686107432e-29</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8723404713710914</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Сир твердий</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0002037602760846932</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3489522548733358</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9255256838346126</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9791246197782543</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Сметана</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>51</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.0002863434322670274</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8956552864195457</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.100370397174733</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.991164062063931e-230</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.988665326159806</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -427,9 +576,5185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>standardized_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ConsumerUA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>producer</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>d_consumer</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>d_retail</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>d_producer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>synthetic_consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12.26030610671325</v>
+      </c>
+      <c r="D2" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.29458180133282</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12.22545920314839</v>
+      </c>
+      <c r="D3" t="n">
+        <v>69.72942962282967</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17.27029049853756</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.002846300832314963</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05311923136862617</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.001405548765441633</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.002622784852425</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12.17781139623318</v>
+      </c>
+      <c r="D4" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17.23707586002156</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.003905039471731708</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.05311923136862617</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.001925075847772462</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12.12589662153451</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.20088677626533</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.004272175556160551</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.002101697911658817</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12.0782488146193</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65.77340576597314</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.16767213774934</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.003937165936391374</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.005287641091787698</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.00193285083262662</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.002586648161224</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12.04340191105444</v>
+      </c>
+      <c r="D7" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.14338083495407</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.002889265598160495</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005287641091787698</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.001415946451604366</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12.02988984640684</v>
+      </c>
+      <c r="D8" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17.13396175835998</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.001122577352753229</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.0005495803419139911</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12.04766659962209</v>
+      </c>
+      <c r="D9" t="n">
+        <v>72.13430734736251</v>
+      </c>
+      <c r="E9" t="n">
+        <v>17.13839517816755</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001476624630507128</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0870265311452787</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0002587169502530351</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.002643764104885</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12.09379690902404</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69.72942962282967</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.14996158451975</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.003821671004369698</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.03390729977665252</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0006746550656226979</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.002622784852425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12.15748084924699</v>
+      </c>
+      <c r="D11" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.16606019781085</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005252019068376246</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.05311923136862617</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0009382564549129668</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12.22791849492526</v>
+      </c>
+      <c r="D12" t="n">
+        <v>67.62516161386344</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.1840902384351</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.005777050487029367</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.02247689698268651</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.001049779523587535</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.002603826089273</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12.29430992069313</v>
+      </c>
+      <c r="D13" t="n">
+        <v>67.92577132943005</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.20145092678676</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.005414808708227969</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.004435383834761275</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.001009766851908456</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.002606570289849</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12.34585520118491</v>
+      </c>
+      <c r="D14" t="n">
+        <v>65.53291799351986</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.21554148326009</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.004183848235325804</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.03586292966797267</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0008188139796012628</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.002584381879199</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12.37175441103492</v>
+      </c>
+      <c r="D15" t="n">
+        <v>64.91967417376404</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.22376112824935</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.002095608736809584</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.009401857439002015</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0004773409751090973</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.002578565027031</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>12.38075113140858</v>
+      </c>
+      <c r="D16" t="n">
+        <v>82.09036828878632</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.2287415375809</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.000726934148497449</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2346699690072933</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.00028911742142812</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.002723763506183</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12.38870578114559</v>
+      </c>
+      <c r="D17" t="n">
+        <v>65.77340576597314</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.23447827577908</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0006422950683631079</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2216051038095541</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0003329194591938922</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.002586648161224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12.39549369139163</v>
+      </c>
+      <c r="D18" t="n">
+        <v>64.91967417376404</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.24041639628513</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0005477611187951759</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.01306486519773919</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0003444895551534266</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.002578565027031</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12.40099019329236</v>
+      </c>
+      <c r="D19" t="n">
+        <v>127.6593787064812</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.24600095254028</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0004433291442702547</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6762148892876807</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0003238699020240432</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.002997019727808</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12.40507061799348</v>
+      </c>
+      <c r="D20" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.25067699798576</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0003289861110125081</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.6578623829981538</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0002711012046336947</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12.40761029664065</v>
+      </c>
+      <c r="D21" t="n">
+        <v>67.92577132943005</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.25388958606282</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0002047081220104552</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.02691228081744779</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0001862123425611095</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.002606570289849</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12.40848456037956</v>
+      </c>
+      <c r="D22" t="n">
+        <v>66.42272275159704</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17.25508377021267</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.045941307914916e-05</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.02237630279607927</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.921006533611163e-05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.002592726003676</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12.39886369761992</v>
+      </c>
+      <c r="D23" t="n">
+        <v>67.32455189829686</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17.24810262339262</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.000775646243357464</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01348577481971081</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.0004046667942887439</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.00260106967043</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>12.37342900878686</v>
+      </c>
+      <c r="D24" t="n">
+        <v>111.1361338563342</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17.2296617635476</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.002053479512147405</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5012308981221665</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.00106972490423507</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.002911231147165</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12.33732234304916</v>
+      </c>
+      <c r="D25" t="n">
+        <v>68.17227129619468</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.2035150616003</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.002922346708106538</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.4887179780591655</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.001518692690222867</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.00260881149276</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12.29568554957562</v>
+      </c>
+      <c r="D26" t="n">
+        <v>68.52699076056328</v>
+      </c>
+      <c r="E26" t="n">
+        <v>17.17341638847341</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.003380572385481173</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0051897904231053</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.001751097584825168</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.002612022466269</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12.25366047753503</v>
+      </c>
+      <c r="D27" t="n">
+        <v>67.32455189829686</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.14311961508963</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.003423725670354205</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.01770271048610628</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.001765724911873434</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.00260106967043</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12.21638897609617</v>
+      </c>
+      <c r="D28" t="n">
+        <v>74.50184903715595</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.11637861237165</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.003046297910640927</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1012989614922182</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.001561085802895157</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.00266374569191</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12.18901289442783</v>
+      </c>
+      <c r="D29" t="n">
+        <v>66.72333246716366</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.09694725124218</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.002243445389316978</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.1102692405152101</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.001135894434596718</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.002595519739177</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>12.17138203951479</v>
+      </c>
+      <c r="D30" t="n">
+        <v>72.13430734736251</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.08467083668607</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.001447501819185515</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.07797505732719134</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.0007183050873940111</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.002643764104885</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12.15836241962987</v>
+      </c>
+      <c r="D31" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17.07575575853077</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.001070263697144469</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.0870265311452787</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.0005219535729654723</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12.14762018587395</v>
+      </c>
+      <c r="D32" t="n">
+        <v>72.13430734736251</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.06849751496284</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.0008839169047134554</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0870265311452787</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.0004251517008806438</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.002643764104885</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12.1368214893479</v>
+      </c>
+      <c r="D33" t="n">
+        <v>72.13430734736251</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.06119160416882</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.000889351081835521</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.0004281264256529305</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.002643764104885</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>12.12363248115259</v>
+      </c>
+      <c r="D34" t="n">
+        <v>59.80455715535038</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.05213352433528</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.001087284641142272</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.1874478965159652</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.0005310581722715035</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.002527791129331</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>12.1057193123889</v>
+      </c>
+      <c r="D35" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.03961877364875</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.001478634028681203</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1004213653706865</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.0007341805806451163</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>12.08074813415769</v>
+      </c>
+      <c r="D36" t="n">
+        <v>65.67784016179655</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17.0219428502958</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.002064889150017901</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.006741649691534235</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.001037881065748092</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.002585748573776</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>11.95312133463902</v>
+      </c>
+      <c r="D37" t="n">
+        <v>67.87166158062809</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.83634990008948</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.0106206784023164</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.03285701188532197</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-0.01096303410274091</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.002606077230604</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11.67108771163957</v>
+      </c>
+      <c r="D38" t="n">
+        <v>68.38671783664532</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.39122282451126</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.02387779607114249</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.007560029868943552</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.02679423560839878</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.002610754684839</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11.29808303070008</v>
+      </c>
+      <c r="D39" t="n">
+        <v>69.72942962282967</v>
+      </c>
+      <c r="E39" t="n">
+        <v>15.79156525525032</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.03248157972473109</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.01944383930589488</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.03727004505281517</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.002622784852425</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10.89754305736136</v>
+      </c>
+      <c r="D40" t="n">
+        <v>90.29107670051859</v>
+      </c>
+      <c r="E40" t="n">
+        <v>15.14238082399583</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.03609571178089999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.258416175759125</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.04197846333985522</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.002782684160107</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>10.53290355716416</v>
+      </c>
+      <c r="D41" t="n">
+        <v>72.13430734736251</v>
+      </c>
+      <c r="E41" t="n">
+        <v>14.54867316243697</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.03403332668816139</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.2245088759824725</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.03999769166868239</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.002643764104885</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10.26760029564928</v>
+      </c>
+      <c r="D42" t="n">
+        <v>69.4288199072631</v>
+      </c>
+      <c r="E42" t="n">
+        <v>14.11544590226293</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.02551069449256627</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.0382277074302122</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.03023014600085627</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.00262011174503</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>10.16506903835748</v>
+      </c>
+      <c r="D43" t="n">
+        <v>54.68873084674468</v>
+      </c>
+      <c r="E43" t="n">
+        <v>13.94770267516288</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.0100360962359729</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.2386443829735141</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.01195483995169955</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.002472469602045</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10.17474982602348</v>
+      </c>
+      <c r="D44" t="n">
+        <v>66.59394237166215</v>
+      </c>
+      <c r="E44" t="n">
+        <v>13.95176704371934</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0009519050746269464</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1969559472527447</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0002913581244494701</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.002594318789175</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>10.19971606789896</v>
+      </c>
+      <c r="D45" t="n">
+        <v>68.52699076056328</v>
+      </c>
+      <c r="E45" t="n">
+        <v>13.96224883631231</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.002450739518898182</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.02861407533288851</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.000751005740676991</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.002612022466269</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10.23385358230012</v>
+      </c>
+      <c r="D46" t="n">
+        <v>66.1221130360304</v>
+      </c>
+      <c r="E46" t="n">
+        <v>13.9765810833272</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.003341319871761339</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.0357244633271856</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.001025973407856373</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.002589919603668</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10.30518570194435</v>
+      </c>
+      <c r="D47" t="n">
+        <v>315.98280122438</v>
+      </c>
+      <c r="E47" t="n">
+        <v>14.00652906216427</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.006946031453140655</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.564184555565703</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.002140433291020649</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.003558143142253</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10.33983273148583</v>
+      </c>
+      <c r="D48" t="n">
+        <v>67.44625655822406</v>
+      </c>
+      <c r="E48" t="n">
+        <v>14.02107522331371</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.003356457363350884</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-1.544356703994426</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.001037988285213398</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.00260218711138</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10.30449439228249</v>
+      </c>
+      <c r="D49" t="n">
+        <v>47.7860221572009</v>
+      </c>
+      <c r="E49" t="n">
+        <v>13.99826880802143</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.003423543282099484</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.3445979083623798</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.001627905371612837</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.002389005471448</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>10.26505257993789</v>
+      </c>
+      <c r="D50" t="n">
+        <v>67.92577132943005</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13.97272055097166</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.00383497611660788</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3516823376085507</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.001826768715728733</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.002606570289849</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10.21530110501763</v>
+      </c>
+      <c r="D51" t="n">
+        <v>66.42683658905966</v>
+      </c>
+      <c r="E51" t="n">
+        <v>13.94037316059995</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.004858468125076509</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.02231437052495444</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.002317722656353993</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.002592764321095</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10.15839404196142</v>
+      </c>
+      <c r="D52" t="n">
+        <v>106.8743578559484</v>
+      </c>
+      <c r="E52" t="n">
+        <v>13.90319981161669</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.005586341666365957</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.4755527785460787</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.002670158108423859</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.002887031418553</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>9.830279131724351</v>
+      </c>
+      <c r="D53" t="n">
+        <v>156.3322725994447</v>
+      </c>
+      <c r="E53" t="n">
+        <v>13.68103755682871</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.0328330332616904</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.3803297758034931</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.01610826180299707</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.00312243767352</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>9.691803781082035</v>
+      </c>
+      <c r="D54" t="n">
+        <v>88.04973675567888</v>
+      </c>
+      <c r="E54" t="n">
+        <v>13.58445244569546</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-0.0141867723610738</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.5740818494532647</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.007084817850592451</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.002767129232367</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>9.553179395806762</v>
+      </c>
+      <c r="D55" t="n">
+        <v>64.67411284436368</v>
+      </c>
+      <c r="E55" t="n">
+        <v>13.48737283686182</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.01440653718401119</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.3085408343796159</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.007172033946905909</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.002576220372252</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9.351387600722028</v>
+      </c>
+      <c r="D56" t="n">
+        <v>53.18882963323848</v>
+      </c>
+      <c r="E56" t="n">
+        <v>13.33383547086344</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.02134928132984104</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.1955126058431609</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.01144907726680167</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.002455266255388</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>9.395634984930259</v>
+      </c>
+      <c r="D57" t="n">
+        <v>62.35660069957631</v>
+      </c>
+      <c r="E57" t="n">
+        <v>13.35513669416056</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.004720479336862038</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1590211267916515</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.001596256887558489</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.002553643765633</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9.454772656359481</v>
+      </c>
+      <c r="D58" t="n">
+        <v>60.39479836396756</v>
+      </c>
+      <c r="E58" t="n">
+        <v>13.38858888106316</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.006274438894724454</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.03196655036219731</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.002501686180934826</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.002533867066874</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>58.18572331087821</v>
+      </c>
+      <c r="D59" t="n">
+        <v>156.4197360688442</v>
+      </c>
+      <c r="E59" t="n">
+        <v>59.7425009860533</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>1.00103003768343</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>58.13212230625698</v>
+      </c>
+      <c r="D60" t="n">
+        <v>166.2729477897163</v>
+      </c>
+      <c r="E60" t="n">
+        <v>59.7161802817836</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.0009216300066583472</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.06108769197983843</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.0004406662524019112</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.001042497827092</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>58.05883113667285</v>
+      </c>
+      <c r="D61" t="n">
+        <v>149.7621605817685</v>
+      </c>
+      <c r="E61" t="n">
+        <v>59.67715235621521</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.001261564297958095</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.1045822622414816</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.0006537706268208154</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.001021166128424</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>57.97897657876775</v>
+      </c>
+      <c r="D62" t="n">
+        <v>163.0773115559199</v>
+      </c>
+      <c r="E62" t="n">
+        <v>59.6293771397054</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-0.001376354346628084</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.08517595279740231</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.00080088188409011</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.001038539477666</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>57.90568540918363</v>
+      </c>
+      <c r="D63" t="n">
+        <v>164.0759478789814</v>
+      </c>
+      <c r="E63" t="n">
+        <v>59.57681456261143</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.001264898703569273</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.006105025066803549</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.0008818766835823055</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.001039784731937</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>57.85208440456239</v>
+      </c>
+      <c r="D64" t="n">
+        <v>169.7348870429957</v>
+      </c>
+      <c r="E64" t="n">
+        <v>59.52342455529058</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.0009260891694502504</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.03390831434977759</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-0.0008965558976639088</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.001046701107371</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>57.831300341546</v>
+      </c>
+      <c r="D65" t="n">
+        <v>173.8958717224181</v>
+      </c>
+      <c r="E65" t="n">
+        <v>59.47316704810014</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-0.0003593266792050187</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.02421894990111184</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-0.0008446882301669234</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.001051641144802</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>57.88122128717562</v>
+      </c>
+      <c r="D66" t="n">
+        <v>154.7553421970754</v>
+      </c>
+      <c r="E66" t="n">
+        <v>59.41572623700268</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.0008628443667832997</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.1166112492656826</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.000966294057918482</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1.001027855699265</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>58.01299688011047</v>
+      </c>
+      <c r="D67" t="n">
+        <v>163.0773115559199</v>
+      </c>
+      <c r="E67" t="n">
+        <v>59.3438108669743</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.002274067711179661</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.05237895994798958</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.001211109112959186</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.001038539477666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>58.19964625441952</v>
+      </c>
+      <c r="D68" t="n">
+        <v>177.2246594659559</v>
+      </c>
+      <c r="E68" t="n">
+        <v>59.26591769189249</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.003212207033008951</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.08319379787642767</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.001313436717647498</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.001055508817615</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>58.41418854417175</v>
+      </c>
+      <c r="D69" t="n">
+        <v>178.0568564018404</v>
+      </c>
+      <c r="E69" t="n">
+        <v>59.19054346563472</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.003679538232836954</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.004684727016248225</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.0012726065880031</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1.001056464386889</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>58.62964288343613</v>
+      </c>
+      <c r="D70" t="n">
+        <v>179.4216593766909</v>
+      </c>
+      <c r="E70" t="n">
+        <v>59.12618494207847</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.003681605087528794</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.007635757371792451</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0.001087902459270929</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.001058021895846</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>58.81902840628162</v>
+      </c>
+      <c r="D71" t="n">
+        <v>183.0500380171469</v>
+      </c>
+      <c r="E71" t="n">
+        <v>59.08133887510123</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.003224994968597628</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.02002087260477037</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-0.0007587684384313675</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.001062105678862</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>58.95536424677721</v>
+      </c>
+      <c r="D72" t="n">
+        <v>193.0364012477607</v>
+      </c>
+      <c r="E72" t="n">
+        <v>59.06450201858049</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.002315204490942691</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.05311923136862706</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.0002850181861226986</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.001072940822544</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>59.05792367883593</v>
+      </c>
+      <c r="D73" t="n">
+        <v>208.6252614492245</v>
+      </c>
+      <c r="E73" t="n">
+        <v>59.08748167713054</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.001738100169577983</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.07766085656093136</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0003889847317157802</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.001088782123883</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>59.16020162202844</v>
+      </c>
+      <c r="D74" t="n">
+        <v>158.9076527803726</v>
+      </c>
+      <c r="E74" t="n">
+        <v>59.14674500707543</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.001730326351409239</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.272216401815947</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.001002473421952033</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.001033256383271</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>59.25654967891018</v>
+      </c>
+      <c r="D75" t="n">
+        <v>277.0504798632544</v>
+      </c>
+      <c r="E75" t="n">
+        <v>59.2277785398572</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.001627271092715432</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.5558764939904721</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.001369104483151418</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.001146645384918</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>59.34131945203654</v>
+      </c>
+      <c r="D76" t="n">
+        <v>156.4197360688442</v>
+      </c>
+      <c r="E76" t="n">
+        <v>59.31606880691795</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.001429533063006083</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.5716567175090814</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.001489580190994211</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.00103003768343</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>59.40886254396295</v>
+      </c>
+      <c r="D77" t="n">
+        <v>174.9892250345743</v>
+      </c>
+      <c r="E77" t="n">
+        <v>59.39710233969972</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.001137566243265553</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1121813909484715</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.001365198900589171</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.001052919600855</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>59.45353055724483</v>
+      </c>
+      <c r="D78" t="n">
+        <v>176.092871633153</v>
+      </c>
+      <c r="E78" t="n">
+        <v>59.4563656696446</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.0007515920590046576</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.006287134801057803</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0009972504100881352</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1.001054202018861</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>59.46967509443758</v>
+      </c>
+      <c r="D79" t="n">
+        <v>263.4826762361423</v>
+      </c>
+      <c r="E79" t="n">
+        <v>59.47934532819466</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.000271511976211336</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.402976085387774</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0003864215153415174</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.001136402473064</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>59.46654802491421</v>
+      </c>
+      <c r="D80" t="n">
+        <v>140.6668636723298</v>
+      </c>
+      <c r="E80" t="n">
+        <v>59.47765779304346</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-5.258397218455002e-05</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-0.6275931951046418</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-2.837218670670438e-05</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.001008386774252</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>59.4577272569145</v>
+      </c>
+      <c r="D81" t="n">
+        <v>123.4776250870784</v>
+      </c>
+      <c r="E81" t="n">
+        <v>59.4728331242652</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-0.0001483425985986386</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-0.1303344596109426</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-8.112061991027986e-05</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.000981803362055</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>59.44405345129404</v>
+      </c>
+      <c r="D82" t="n">
+        <v>213.2670589364177</v>
+      </c>
+      <c r="E82" t="n">
+        <v>59.46522822687292</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-0.0002300016971874541</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.5464852119146961</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.000127879962330546</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.001093270871406</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>59.42636726890843</v>
+      </c>
+      <c r="D83" t="n">
+        <v>183.0500380171469</v>
+      </c>
+      <c r="E83" t="n">
+        <v>59.45520000587967</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-0.0002975707902592717</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-0.1527856309314171</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.0001686543038239563</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1.001062105678862</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>59.40550937061328</v>
+      </c>
+      <c r="D84" t="n">
+        <v>215.1529820013891</v>
+      </c>
+      <c r="E84" t="n">
+        <v>59.44310536629845</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-0.0003510488784526089</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.1615897720391706</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.0002034451136214699</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1.001095066768495</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>59.38232041726418</v>
+      </c>
+      <c r="D85" t="n">
+        <v>168.8277122465017</v>
+      </c>
+      <c r="E85" t="n">
+        <v>59.42930121314233</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-0.0003904264213776543</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-0.242470578529093</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.0002322515984225504</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.001045608015529</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>59.35764106971671</v>
+      </c>
+      <c r="D86" t="n">
+        <v>174.3608241533142</v>
+      </c>
+      <c r="E86" t="n">
+        <v>59.41414445142431</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-0.0004156873152689755</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0322481133293433</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.0002550710595006223</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.001052185792185</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>59.33029275953629</v>
+      </c>
+      <c r="D87" t="n">
+        <v>176.3924625300714</v>
+      </c>
+      <c r="E87" t="n">
+        <v>59.39508401203917</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-0.0004608439928492913</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.01158455914552814</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.000320857896228155</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.0010545487516</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>59.29681789397659</v>
+      </c>
+      <c r="D88" t="n">
+        <v>206.2017567734527</v>
+      </c>
+      <c r="E88" t="n">
+        <v>59.36827583041003</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-0.0005643712683180979</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.1561436780630299</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.0004514554340673271</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1.00108639868861</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>59.25463859742558</v>
+      </c>
+      <c r="D89" t="n">
+        <v>177.2139480371479</v>
+      </c>
+      <c r="E89" t="n">
+        <v>59.33213731834251</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-0.0007115779017672352</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-0.1514973427002735</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.000608902904807529</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.001055496489007</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>59.20117699427127</v>
+      </c>
+      <c r="D90" t="n">
+        <v>164.6479771293256</v>
+      </c>
+      <c r="E90" t="n">
+        <v>59.2850858876422</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-0.0009026421626856518</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-0.07354802573748831</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.0007933322311277635</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1.001040494617542</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>59.13385520890166</v>
+      </c>
+      <c r="D91" t="n">
+        <v>134.2651723867601</v>
+      </c>
+      <c r="E91" t="n">
+        <v>59.22553895011469</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-0.001137816779684719</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-0.2039929799442346</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.001004921586064356</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1.000998886567517</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>59.05009536570473</v>
+      </c>
+      <c r="D92" t="n">
+        <v>173.0636747865336</v>
+      </c>
+      <c r="E92" t="n">
+        <v>59.15191391756561</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-0.001417448931325005</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.2538428462099205</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0.001243903129503288</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1.001050662660439</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>58.94731958906848</v>
+      </c>
+      <c r="D93" t="n">
+        <v>179.7212502736093</v>
+      </c>
+      <c r="E93" t="n">
+        <v>59.06262820180054</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-0.001742000918675046</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.03774745183457107</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.001510571053986887</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.001058362202356</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>58.26309647166663</v>
+      </c>
+      <c r="D94" t="n">
+        <v>174.8235318946889</v>
+      </c>
+      <c r="E94" t="n">
+        <v>58.33124123658099</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-0.01167525741615538</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-0.02762996498003112</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.01246055576759897</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.001052726370466</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>56.67383846597856</v>
+      </c>
+      <c r="D95" t="n">
+        <v>165.6240332294588</v>
+      </c>
+      <c r="E95" t="n">
+        <v>56.59676243679495</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-0.02765619776817818</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-0.05405671636559717</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.03018603728673241</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1.001041700224368</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>54.53523348610081</v>
+      </c>
+      <c r="D96" t="n">
+        <v>183.8822349530316</v>
+      </c>
+      <c r="E96" t="n">
+        <v>54.25578418593767</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-0.03846572276763416</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.1045751656565237</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0.04224217513386685</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1.001063030913077</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>52.20296944612988</v>
+      </c>
+      <c r="D97" t="n">
+        <v>169.9239532160398</v>
+      </c>
+      <c r="E97" t="n">
+        <v>51.70489886750449</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-0.04370759955882253</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-0.07894452233156635</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-0.04815707499282684</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1.001046928185266</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>50.03273426016229</v>
+      </c>
+      <c r="D98" t="n">
+        <v>166.1065084025394</v>
+      </c>
+      <c r="E98" t="n">
+        <v>49.34069886499066</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-0.04246190279331108</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-0.02272180345205221</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-0.0468032574140258</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1.001042293547981</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>48.38021584229453</v>
+      </c>
+      <c r="D99" t="n">
+        <v>164.0759478789814</v>
+      </c>
+      <c r="E99" t="n">
+        <v>47.5597765618915</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-0.03358650985150291</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-0.012299782040186</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-0.03676190148333625</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1.001039784731937</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>47.60110210662313</v>
+      </c>
+      <c r="D100" t="n">
+        <v>191.7455896122293</v>
+      </c>
+      <c r="E100" t="n">
+        <v>46.75872434170228</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-0.01623505209719855</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.1558400218133382</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-0.01698651852698463</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1.001071572259825</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>47.39002349439211</v>
+      </c>
+      <c r="D101" t="n">
+        <v>177.1938808250335</v>
+      </c>
+      <c r="E101" t="n">
+        <v>46.59072442286183</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-0.004444182723575274</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-0.07892493427974134</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-0.003599380659260465</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1.001055473390101</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>47.20584056134357</v>
+      </c>
+      <c r="D102" t="n">
+        <v>291.3776058367948</v>
+      </c>
+      <c r="E102" t="n">
+        <v>46.4453473356251</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-0.003894106103555561</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.4973755355721412</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-0.003125179359160235</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1.001156930874932</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>47.05058639332115</v>
+      </c>
+      <c r="D103" t="n">
+        <v>203.0275921379999</v>
+      </c>
+      <c r="E103" t="n">
+        <v>46.32376793121173</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-0.003294296494044335</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-0.3612781488894372</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-0.002621119618756218</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1.001083234285693</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>46.92629407616848</v>
+      </c>
+      <c r="D104" t="n">
+        <v>207.9528112222201</v>
+      </c>
+      <c r="E104" t="n">
+        <v>46.22716106084129</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-0.002645169514111867</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.02396929317136731</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-0.002087648530580299</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1.001088123577933</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>46.83499669572922</v>
+      </c>
+      <c r="D105" t="n">
+        <v>78.07647108306644</v>
+      </c>
+      <c r="E105" t="n">
+        <v>46.15670157573338</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-0.00194744352475773</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-0.9796224399249676</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-0.001525363775853439</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.000888318182847</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>46.85359373147352</v>
+      </c>
+      <c r="D106" t="n">
+        <v>315.4301448142353</v>
+      </c>
+      <c r="E106" t="n">
+        <v>46.16855757255477</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0003969968147403691</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.396248501504124</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0002568310556814168</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.001173111399413</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>46.95664174753841</v>
+      </c>
+      <c r="D107" t="n">
+        <v>191.7750813948186</v>
+      </c>
+      <c r="E107" t="n">
+        <v>46.24510975770006</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.002196946995946192</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-0.4976140121438464</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.001656729028649995</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1.00107160363072</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>47.08410108188146</v>
+      </c>
+      <c r="D108" t="n">
+        <v>175.2537601436198</v>
+      </c>
+      <c r="E108" t="n">
+        <v>46.34016153275736</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.002710727468886454</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-0.09008825270576093</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.002053281415651309</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1.001053227721342</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>47.22627487595583</v>
+      </c>
+      <c r="D109" t="n">
+        <v>242.6582994673198</v>
+      </c>
+      <c r="E109" t="n">
+        <v>46.44671984918083</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.003015021419038089</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.3254192971487981</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.002296841141375516</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.001119607284805</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46005</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>47.37346627121473</v>
+      </c>
+      <c r="D110" t="n">
+        <v>242.0801190756869</v>
+      </c>
+      <c r="E110" t="n">
+        <v>46.55779165842463</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.003111879847764953</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-0.002385536791420506</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.002388526325212581</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.001119120663072</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>47.91504497381387</v>
+      </c>
+      <c r="D111" t="n">
+        <v>225.0068366341545</v>
+      </c>
+      <c r="E111" t="n">
+        <v>46.98042772371997</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.01136725775572067</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-0.07313795514212007</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.009036711286515509</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1.001104201486489</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>48.16497351955958</v>
+      </c>
+      <c r="D112" t="n">
+        <v>216.132735226714</v>
+      </c>
+      <c r="E112" t="n">
+        <v>47.17997785167286</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.005202520011608591</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-0.04023805289782256</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.004238520968077086</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1.001095993550113</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>48.4098372848281</v>
+      </c>
+      <c r="D113" t="n">
+        <v>200.9740636959272</v>
+      </c>
+      <c r="E113" t="n">
+        <v>47.37634906317265</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.005070976333215071</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-0.07271687049116782</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.004153534728362551</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1.001081160611267</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>48.31054439514148</v>
+      </c>
+      <c r="D114" t="n">
+        <v>220.9513062008287</v>
+      </c>
+      <c r="E114" t="n">
+        <v>47.52320215863082</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-0.0020531954660159</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0947664799132637</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.003094919012516684</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1.001100491318838</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>hard_cheese</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>48.03285600075859</v>
+      </c>
+      <c r="D115" t="n">
+        <v>155.9126144367506</v>
+      </c>
+      <c r="E115" t="n">
+        <v>47.37749768939897</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-0.005764570530272461</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-0.3486466568756041</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-0.003070674588342648</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.001029375326583</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>35.4712786383205</v>
+      </c>
+      <c r="D116" t="n">
+        <v>93.85689034796897</v>
+      </c>
+      <c r="E116" t="n">
+        <v>25.93843891908274</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>0.9987003389439189</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>35.38011392069133</v>
+      </c>
+      <c r="D117" t="n">
+        <v>95.62810926376392</v>
+      </c>
+      <c r="E117" t="n">
+        <v>25.88125038150793</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-0.002573407935890781</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.01869562772552591</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-0.00220721357322784</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.998694992545585</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>35.25546012311675</v>
+      </c>
+      <c r="D118" t="n">
+        <v>95.62810926376392</v>
+      </c>
+      <c r="E118" t="n">
+        <v>25.80305380972196</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-0.003529494271589328</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-0.00302593341152102</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.998694992545585</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>35.11964329889369</v>
+      </c>
+      <c r="D119" t="n">
+        <v>95.62810926376392</v>
+      </c>
+      <c r="E119" t="n">
+        <v>25.71785455986561</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.003859802294740255</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-0.003307368997035542</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.998694992545585</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>34.99498950131912</v>
+      </c>
+      <c r="D120" t="n">
+        <v>89.42884305848189</v>
+      </c>
+      <c r="E120" t="n">
+        <v>25.63965798807964</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-0.003555717941624348</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-0.06702354735937188</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-0.003045187678840655</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.9987141594367209</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>34.90382478368995</v>
+      </c>
+      <c r="D121" t="n">
+        <v>89.39341868016601</v>
+      </c>
+      <c r="E121" t="n">
+        <v>25.58246945050482</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-0.002608478276871828</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-0.0003961965186531913</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-0.002232963142962952</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.9987142727391219</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>34.86847519930313</v>
+      </c>
+      <c r="D122" t="n">
+        <v>93.4140856190203</v>
+      </c>
+      <c r="E122" t="n">
+        <v>25.56029430328194</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.001013284281011551</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.04399508057296941</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-0.000867186166132683</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.998701691313206</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>34.94553550218356</v>
+      </c>
+      <c r="D123" t="n">
+        <v>105.3698133006355</v>
+      </c>
+      <c r="E123" t="n">
+        <v>25.58736559144695</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.00220758937645682</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.1204340502746737</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.001058554418661206</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.9986672511805578</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>35.14593283218277</v>
+      </c>
+      <c r="D124" t="n">
+        <v>86.77201468478962</v>
+      </c>
+      <c r="E124" t="n">
+        <v>25.65812018764717</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.005718181707525805</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-0.1941920355493307</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.002761399958849609</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.9987227842301799</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>35.42349182133768</v>
+      </c>
+      <c r="D125" t="n">
+        <v>87.92330698005634</v>
+      </c>
+      <c r="E125" t="n">
+        <v>25.75686918944034</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.007866308157327584</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.01318076468592366</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.003841258139380077</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.9987190148323932</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>35.73203710168517</v>
+      </c>
+      <c r="D126" t="n">
+        <v>85.00079576899478</v>
+      </c>
+      <c r="E126" t="n">
+        <v>25.86792369438423</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.00867247335150978</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.03380430446625304</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.004302377599829654</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.9987286821202714</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>36.02539330526215</v>
+      </c>
+      <c r="D127" t="n">
+        <v>79.68713902161025</v>
+      </c>
+      <c r="E127" t="n">
+        <v>25.9755948000366</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.008176375219292709</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-0.06455241301707293</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.004153701893137907</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.9987471429511493</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45963</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>36.25738506410552</v>
+      </c>
+      <c r="D128" t="n">
+        <v>88.54323360058447</v>
+      </c>
+      <c r="E128" t="n">
+        <v>26.0641936039552</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.006419027067220195</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.1053827425723979</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.003405044187896777</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.9987170055554331</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>36.38183701025218</v>
+      </c>
+      <c r="D129" t="n">
+        <v>90.31445251637935</v>
+      </c>
+      <c r="E129" t="n">
+        <v>26.11803120369779</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.003426580416562963</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.01980654964158557</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.002063446663823854</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.998711341372561</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>36.43474965637226</v>
+      </c>
+      <c r="D130" t="n">
+        <v>105.8903501880953</v>
+      </c>
+      <c r="E130" t="n">
+        <v>26.14850361448059</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.001453313258845679</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.159106628898483</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.00116603920047309</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.9986658419809866</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>36.4822453256734</v>
+      </c>
+      <c r="D131" t="n">
+        <v>100.4989612821997</v>
+      </c>
+      <c r="E131" t="n">
+        <v>26.17684482581869</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.001302732676516705</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-0.05225673458484259</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.001083269006489473</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.9986807855020255</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>36.52333136599877</v>
+      </c>
+      <c r="D132" t="n">
+        <v>96.87681859939921</v>
+      </c>
+      <c r="E132" t="n">
+        <v>26.20212289671812</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.001125559074384164</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-0.03670713180895113</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.0009651993523727143</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.998691282537242</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>36.55701512519151</v>
+      </c>
+      <c r="D133" t="n">
+        <v>87.30338035952813</v>
+      </c>
+      <c r="E133" t="n">
+        <v>26.22340588618493</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.0009218281848752952</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-0.1040510768544669</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.0008119323211461804</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.9987210383306183</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>36.58230395109481</v>
+      </c>
+      <c r="D134" t="n">
+        <v>89.87164778743065</v>
+      </c>
+      <c r="E134" t="n">
+        <v>26.23976185322516</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.0006915248112902006</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.02899333345384925</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.0006235219211840892</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.9987127469324266</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45970</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>36.5982051915518</v>
+      </c>
+      <c r="D135" t="n">
+        <v>91.20006197427671</v>
+      </c>
+      <c r="E135" t="n">
+        <v>26.25025885684488</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.0004345758424899593</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.01467305988691336</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.0003999618829504392</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.9987085508153497</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>36.60372619440565</v>
+      </c>
+      <c r="D136" t="n">
+        <v>87.92330698005634</v>
+      </c>
+      <c r="E136" t="n">
+        <v>26.2539649560501</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.000150843092792563</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-0.0365906537216425</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0001411733739584697</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.9987190148323932</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>36.57440372720725</v>
+      </c>
+      <c r="D137" t="n">
+        <v>87.48050225110757</v>
+      </c>
+      <c r="E137" t="n">
+        <v>26.23562122279388</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.0008013997843114851</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.005048985783873583</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.0006989475565877257</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.9987204587253793</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>36.49664515783994</v>
+      </c>
+      <c r="D138" t="n">
+        <v>87.12625846794859</v>
+      </c>
+      <c r="E138" t="n">
+        <v>26.18706221048788</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-0.002128301150879253</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-0.004057623745285177</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.001852595976172378</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.9987216191132979</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>36.38576373464561</v>
+      </c>
+      <c r="D139" t="n">
+        <v>90.31445251637935</v>
+      </c>
+      <c r="E139" t="n">
+        <v>26.11799620032609</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-0.003042750930639215</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.03593918425981624</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-0.002640893726187254</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.998711341372561</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>36.2570727059661</v>
+      </c>
+      <c r="D140" t="n">
+        <v>90.31445251637935</v>
+      </c>
+      <c r="E140" t="n">
+        <v>26.0381314735025</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-0.003543120550193901</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-0.00306252756126657</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.998711341372561</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>36.1258853201433</v>
+      </c>
+      <c r="D141" t="n">
+        <v>88.10042887163578</v>
+      </c>
+      <c r="E141" t="n">
+        <v>25.95717631121112</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-0.003624818135176788</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-0.02482009669180574</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-0.003113943590551838</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.9987184393108705</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>36.00751482551906</v>
+      </c>
+      <c r="D142" t="n">
+        <v>88.98603832953316</v>
+      </c>
+      <c r="E142" t="n">
+        <v>25.88483899464592</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-0.00328199143911645</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.01000208378468415</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-0.002790684856090575</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.9987155789543953</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>35.91727447043525</v>
+      </c>
+      <c r="D143" t="n">
+        <v>93.77718549675822</v>
+      </c>
+      <c r="E143" t="n">
+        <v>25.8308278050009</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.002509299041891122</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.05244211672247445</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-0.002088775515232566</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.998700581898751</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>35.8562702822273</v>
+      </c>
+      <c r="D144" t="n">
+        <v>86.77201468478962</v>
+      </c>
+      <c r="E144" t="n">
+        <v>25.79533079169903</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-0.001699907761513852</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-0.077637443231934</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-0.001375156310702064</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.9987227842301799</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>35.8101493413126</v>
+      </c>
+      <c r="D145" t="n">
+        <v>101.7476706178351</v>
+      </c>
+      <c r="E145" t="n">
+        <v>25.76892866729914</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-0.001287100639994598</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.159211772654845</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-0.001024047547047324</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.9986772542498904</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>35.77103647565598</v>
+      </c>
+      <c r="D146" t="n">
+        <v>86.59489279321015</v>
+      </c>
+      <c r="E146" t="n">
+        <v>25.74691870769899</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-0.001092825415025533</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-0.1612550917147741</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-0.0008544928235059146</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.9987233685740562</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>35.73105651322228</v>
+      </c>
+      <c r="D147" t="n">
+        <v>103.6074504794197</v>
+      </c>
+      <c r="E147" t="n">
+        <v>25.72459818879635</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-0.001118288008894908</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.1793684039090104</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-0.0008672959977711336</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.9986720744959298</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>35.68233428197632</v>
+      </c>
+      <c r="D148" t="n">
+        <v>97.84213290850745</v>
+      </c>
+      <c r="E148" t="n">
+        <v>25.69726438648899</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-0.001364512684892016</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-0.05725395195847316</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-0.0010631199848814</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.9986884471528532</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>35.61699460988294</v>
+      </c>
+      <c r="D149" t="n">
+        <v>106.6982274874817</v>
+      </c>
+      <c r="E149" t="n">
+        <v>25.66021457667469</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-0.001832827640875667</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.08664925495054643</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-0.0014428206753756</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.9986636685567064</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>35.52716232490695</v>
+      </c>
+      <c r="D150" t="n">
+        <v>106.2118829378717</v>
+      </c>
+      <c r="E150" t="n">
+        <v>25.60874603525121</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-0.002525360805105681</v>
+      </c>
+      <c r="G150" t="n">
+        <v>-0.00456855143740853</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-0.002007786313558579</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.998664974984105</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>35.11538037560963</v>
+      </c>
+      <c r="D151" t="n">
+        <v>99.61335182430228</v>
+      </c>
+      <c r="E151" t="n">
+        <v>25.33334565433683</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-0.01165831799189609</v>
+      </c>
+      <c r="G151" t="n">
+        <v>-0.0641397845518199</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-0.01081239716767302</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.9986833166395118</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>34.22188693370104</v>
+      </c>
+      <c r="D152" t="n">
+        <v>97.39932817955869</v>
+      </c>
+      <c r="E152" t="n">
+        <v>24.72003890605964</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-0.02577381363758224</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-0.02247689698268651</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-0.02450733151552642</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.9986897442977037</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>33.04534966186926</v>
+      </c>
+      <c r="D153" t="n">
+        <v>94.66279495465574</v>
+      </c>
+      <c r="E153" t="n">
+        <v>23.90743093633211</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-0.03498455794601529</v>
+      </c>
+      <c r="G153" t="n">
+        <v>-0.02849826279381329</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-0.03342487800728389</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.9986978939292704</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>31.78443622280236</v>
+      </c>
+      <c r="D154" t="n">
+        <v>87.96778951942865</v>
+      </c>
+      <c r="E154" t="n">
+        <v>23.03412689106674</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-0.03890410722972737</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-0.07335033100519528</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-0.03721243435978128</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.998718870186458</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>30.63781427918839</v>
+      </c>
+      <c r="D155" t="n">
+        <v>90.31445251637935</v>
+      </c>
+      <c r="E155" t="n">
+        <v>22.23873191617601</v>
+      </c>
+      <c r="F155" t="n">
+        <v>-0.0367417362295015</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.02632677834635011</v>
+      </c>
+      <c r="H155" t="n">
+        <v>-0.03514144449168155</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.998711341372561</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>29.80415149371543</v>
+      </c>
+      <c r="D156" t="n">
+        <v>89.42884305848189</v>
+      </c>
+      <c r="E156" t="n">
+        <v>21.65985115757242</v>
+      </c>
+      <c r="F156" t="n">
+        <v>-0.02758731111425661</v>
+      </c>
+      <c r="G156" t="n">
+        <v>-0.009854238196240317</v>
+      </c>
+      <c r="H156" t="n">
+        <v>-0.02637507981489007</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.9987141594367209</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>29.48211552907154</v>
+      </c>
+      <c r="D157" t="n">
+        <v>85.88640522689225</v>
+      </c>
+      <c r="E157" t="n">
+        <v>21.43608976116845</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-0.01086386942985618</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-0.04041770575356285</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-0.01038443075760975</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.9987257179667202</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>29.49941385719898</v>
+      </c>
+      <c r="D158" t="n">
+        <v>92.89157603886082</v>
+      </c>
+      <c r="E158" t="n">
+        <v>21.4463485926483</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.000586567652735237</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.07840741029630571</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0004784630757663777</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.9987032953809269</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>29.54402533500134</v>
+      </c>
+      <c r="D159" t="n">
+        <v>94.74249980586642</v>
+      </c>
+      <c r="E159" t="n">
+        <v>21.47280557909632</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.001511141183578868</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.01972971912959132</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.001232875638383923</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.9986976532470723</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>29.60502470260863</v>
+      </c>
+      <c r="D160" t="n">
+        <v>97.39932817955869</v>
+      </c>
+      <c r="E160" t="n">
+        <v>21.50898145852524</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.002062565305568587</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.0276566299765646</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.001683312419719307</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.9986897442977037</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>29.73248606775821</v>
+      </c>
+      <c r="D161" t="n">
+        <v>94.5905325685591</v>
+      </c>
+      <c r="E161" t="n">
+        <v>21.58457284837673</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.004296154642832839</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-0.02926192059105404</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.003508249370359096</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.9986981123129596</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>29.55008214822241</v>
+      </c>
+      <c r="D162" t="n">
+        <v>87.65762414268707</v>
+      </c>
+      <c r="E162" t="n">
+        <v>21.47436524442937</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-0.00615373121093743</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-0.07611880096487411</v>
+      </c>
+      <c r="H162" t="n">
+        <v>-0.005118929982030007</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.9987198802928172</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>29.38929750480896</v>
+      </c>
+      <c r="D163" t="n">
+        <v>96.96112364853489</v>
+      </c>
+      <c r="E163" t="n">
+        <v>21.37738112631663</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-0.005455946201136097</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.1008715195099414</v>
+      </c>
+      <c r="H163" t="n">
+        <v>-0.004526503207956001</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.9986910337871504</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46004</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>29.20711270834541</v>
+      </c>
+      <c r="D164" t="n">
+        <v>91.20006197427671</v>
+      </c>
+      <c r="E164" t="n">
+        <v>21.26719822016227</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-0.006218312106545554</v>
+      </c>
+      <c r="G164" t="n">
+        <v>-0.06125453441568673</v>
+      </c>
+      <c r="H164" t="n">
+        <v>-0.00516751029222462</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.9987085508153497</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>28.57099212612363</v>
+      </c>
+      <c r="D165" t="n">
+        <v>122.3074863313084</v>
+      </c>
+      <c r="E165" t="n">
+        <v>20.87781169659026</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-0.02202032372386942</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.2934826770451178</v>
+      </c>
+      <c r="H165" t="n">
+        <v>-0.01847894232976222</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.9986246260340345</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>27.44539411731308</v>
+      </c>
+      <c r="D166" t="n">
+        <v>114.7797136689721</v>
+      </c>
+      <c r="E166" t="n">
+        <v>20.17346658361763</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-0.04019357963245662</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-0.0635234955978925</v>
+      </c>
+      <c r="H166" t="n">
+        <v>-0.03431874822020253</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.9986427907175827</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>sour_cream</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>27.1167501792202</v>
+      </c>
+      <c r="D167" t="n">
+        <v>171.247418352322</v>
+      </c>
+      <c r="E167" t="n">
+        <v>19.90453730281067</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-0.01204673741574958</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.4000946436440049</v>
+      </c>
+      <c r="H167" t="n">
+        <v>-0.01342049459119998</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.9985283882854091</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>